--- a/Employee_Reports_wi52/Romie Ross Tamayo Eleosida Q0605.xlsx
+++ b/Employee_Reports_wi52/Romie Ross Tamayo Eleosida Q0605.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>660</v>
+        <v>652</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -961,11 +961,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1010,11 +1010,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1059,11 +1059,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1108,11 +1108,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-29</v>
+        <v>-37</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1207,11 +1207,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1256,11 +1256,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1305,11 +1305,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1354,11 +1354,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1391,11 +1391,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1428,11 +1428,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1477,11 +1477,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1514,11 +1514,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1551,11 +1551,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1564,6 +1564,43 @@
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>IS0 55001 (Other Trainings)</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr"/>
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>25-Aug-2026</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>24-Aug-2028</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>727</v>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2013,7 +2050,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7907</v>
+        <v>7899</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2108,7 +2145,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7927</v>
+        <v>7919</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2137,7 +2174,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7928</v>
+        <v>7920</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2166,7 +2203,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7927</v>
+        <v>7919</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2195,7 +2232,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7899</v>
+        <v>7891</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2224,7 +2261,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7924</v>
+        <v>7916</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2253,7 +2290,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7902</v>
+        <v>7894</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2282,7 +2319,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7908</v>
+        <v>7900</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2311,7 +2348,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7924</v>
+        <v>7916</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2340,7 +2377,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7924</v>
+        <v>7916</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2369,7 +2406,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7925</v>
+        <v>7917</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2398,7 +2435,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7925</v>
+        <v>7917</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2427,7 +2464,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7978</v>
+        <v>7970</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2456,7 +2493,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7978</v>
+        <v>7970</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2485,7 +2522,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7978</v>
+        <v>7970</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -2514,7 +2551,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7978</v>
+        <v>7970</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
